--- a/data/nzd0078/nzd0078.xlsx
+++ b/data/nzd0078/nzd0078.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I349"/>
+  <dimension ref="A1:I350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11957,6 +11957,39 @@
         <v>345.45</v>
       </c>
       <c r="I349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="C350" t="n">
+        <v>349.07</v>
+      </c>
+      <c r="D350" t="n">
+        <v>353.82</v>
+      </c>
+      <c r="E350" t="n">
+        <v>347.29</v>
+      </c>
+      <c r="F350" t="n">
+        <v>349.37</v>
+      </c>
+      <c r="G350" t="n">
+        <v>350.34</v>
+      </c>
+      <c r="H350" t="n">
+        <v>342.86</v>
+      </c>
+      <c r="I350" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11973,7 +12006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B352"/>
+  <dimension ref="A1:B353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15496,6 +15529,16 @@
       </c>
       <c r="B352" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -15664,28 +15707,28 @@
         <v>0.1223</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4625938077568952</v>
+        <v>0.4631038059876698</v>
       </c>
       <c r="J2" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K2" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L2" t="n">
-        <v>0.329821167012457</v>
+        <v>0.3317055944535396</v>
       </c>
       <c r="M2" t="n">
-        <v>3.829148334154314</v>
+        <v>3.820059128546878</v>
       </c>
       <c r="N2" t="n">
-        <v>23.99872246174863</v>
+        <v>23.93220092992398</v>
       </c>
       <c r="O2" t="n">
-        <v>4.898849095629363</v>
+        <v>4.892054878057276</v>
       </c>
       <c r="P2" t="n">
-        <v>334.6132232556543</v>
+        <v>334.6077317773443</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15742,28 +15785,28 @@
         <v>0.1217</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5086766639516587</v>
+        <v>0.5094764419399991</v>
       </c>
       <c r="J3" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K3" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3938445676897635</v>
+        <v>0.3960653757600602</v>
       </c>
       <c r="M3" t="n">
-        <v>3.693823901951694</v>
+        <v>3.68690490229097</v>
       </c>
       <c r="N3" t="n">
-        <v>21.97956439825566</v>
+        <v>21.92210108854068</v>
       </c>
       <c r="O3" t="n">
-        <v>4.688236811238919</v>
+        <v>4.682104344046668</v>
       </c>
       <c r="P3" t="n">
-        <v>334.0147428684056</v>
+        <v>334.0061311454411</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15820,28 +15863,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4365477889290666</v>
+        <v>0.4375769858157667</v>
       </c>
       <c r="J4" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K4" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L4" t="n">
-        <v>0.24918888621575</v>
+        <v>0.2512194103622026</v>
       </c>
       <c r="M4" t="n">
-        <v>3.814812199189365</v>
+        <v>3.807217890056311</v>
       </c>
       <c r="N4" t="n">
-        <v>31.69143610113009</v>
+        <v>31.60976312289693</v>
       </c>
       <c r="O4" t="n">
-        <v>5.629514730518971</v>
+        <v>5.622256052768935</v>
       </c>
       <c r="P4" t="n">
-        <v>340.3037794522032</v>
+        <v>340.2926974287</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15898,28 +15941,28 @@
         <v>0.1175</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4026871101861665</v>
+        <v>0.4034353527173896</v>
       </c>
       <c r="J5" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K5" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3172693659809395</v>
+        <v>0.3194099384262599</v>
       </c>
       <c r="M5" t="n">
-        <v>3.27732002120131</v>
+        <v>3.270510928811928</v>
       </c>
       <c r="N5" t="n">
-        <v>19.25896820423348</v>
+        <v>19.20861240785691</v>
       </c>
       <c r="O5" t="n">
-        <v>4.388504096412976</v>
+        <v>4.382763101954851</v>
       </c>
       <c r="P5" t="n">
-        <v>335.1706788491688</v>
+        <v>335.1626220415509</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15976,28 +16019,28 @@
         <v>0.1334</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4976291381777806</v>
+        <v>0.4971826166281393</v>
       </c>
       <c r="J6" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K6" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4394311800395809</v>
+        <v>0.4405421175712704</v>
       </c>
       <c r="M6" t="n">
-        <v>3.136775409642874</v>
+        <v>3.130471179791396</v>
       </c>
       <c r="N6" t="n">
-        <v>17.43516183851695</v>
+        <v>17.38692353641217</v>
       </c>
       <c r="O6" t="n">
-        <v>4.175543298604022</v>
+        <v>4.169763007223812</v>
       </c>
       <c r="P6" t="n">
-        <v>336.7834366899819</v>
+        <v>336.7882446741215</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16054,28 +16097,28 @@
         <v>0.1117</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5667500532205217</v>
+        <v>0.5658065686229152</v>
       </c>
       <c r="J7" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K7" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4519432498331492</v>
+        <v>0.4526152639763521</v>
       </c>
       <c r="M7" t="n">
-        <v>3.807196725751195</v>
+        <v>3.801809278612834</v>
       </c>
       <c r="N7" t="n">
-        <v>21.49814938623204</v>
+        <v>21.44422560219622</v>
       </c>
       <c r="O7" t="n">
-        <v>4.636609686638723</v>
+        <v>4.630791034175071</v>
       </c>
       <c r="P7" t="n">
-        <v>336.7634452153999</v>
+        <v>336.7736043196692</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16132,28 +16175,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4471196519325503</v>
+        <v>0.4437152832558641</v>
       </c>
       <c r="J8" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K8" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2373599619727421</v>
+        <v>0.2352474128380827</v>
       </c>
       <c r="M8" t="n">
-        <v>4.883319601487119</v>
+        <v>4.883920946772458</v>
       </c>
       <c r="N8" t="n">
-        <v>35.45161018519541</v>
+        <v>35.4499629101701</v>
       </c>
       <c r="O8" t="n">
-        <v>5.954125476104396</v>
+        <v>5.953987143937254</v>
       </c>
       <c r="P8" t="n">
-        <v>336.78166152163</v>
+        <v>336.8183185443788</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16191,7 +16234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I349"/>
+  <dimension ref="A1:I350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32597,6 +32640,53 @@
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-35.45436382153696,174.42793499789823</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-35.45510021461122,174.42812496477563</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-35.45571921210984,174.4286317209857</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-35.45627850655118,174.4292442325169</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-35.45672824893355,174.42998146225526</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-35.45704799520061,174.4308033217246</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-35.45722516615666,174.43170093871677</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0078/nzd0078.xlsx
+++ b/data/nzd0078/nzd0078.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I350"/>
+  <dimension ref="A1:I353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11992,6 +11992,105 @@
       <c r="I350" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>348.07</v>
+      </c>
+      <c r="C351" t="n">
+        <v>347.71</v>
+      </c>
+      <c r="D351" t="n">
+        <v>354.23</v>
+      </c>
+      <c r="E351" t="n">
+        <v>346.73</v>
+      </c>
+      <c r="F351" t="n">
+        <v>350.11</v>
+      </c>
+      <c r="G351" t="n">
+        <v>348.65</v>
+      </c>
+      <c r="H351" t="n">
+        <v>339.55</v>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>348.72</v>
+      </c>
+      <c r="C352" t="n">
+        <v>348.84</v>
+      </c>
+      <c r="D352" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="E352" t="n">
+        <v>348.31</v>
+      </c>
+      <c r="F352" t="n">
+        <v>351.4</v>
+      </c>
+      <c r="G352" t="n">
+        <v>349.51</v>
+      </c>
+      <c r="H352" t="n">
+        <v>341.56</v>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>348.94</v>
+      </c>
+      <c r="C353" t="n">
+        <v>348.38</v>
+      </c>
+      <c r="D353" t="n">
+        <v>355.97</v>
+      </c>
+      <c r="E353" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="F353" t="n">
+        <v>350.85</v>
+      </c>
+      <c r="G353" t="n">
+        <v>348.85</v>
+      </c>
+      <c r="H353" t="n">
+        <v>341.56</v>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12006,7 +12105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15539,6 +15638,36 @@
       </c>
       <c r="B353" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -15707,28 +15836,28 @@
         <v>0.1223</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4631038059876698</v>
+        <v>0.4656246666595238</v>
       </c>
       <c r="J2" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K2" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3317055944535396</v>
+        <v>0.3381830128222215</v>
       </c>
       <c r="M2" t="n">
-        <v>3.820059128546878</v>
+        <v>3.796929177506129</v>
       </c>
       <c r="N2" t="n">
-        <v>23.93220092992398</v>
+        <v>23.74783818773758</v>
       </c>
       <c r="O2" t="n">
-        <v>4.892054878057276</v>
+        <v>4.8731753700988</v>
       </c>
       <c r="P2" t="n">
-        <v>334.6077317773443</v>
+        <v>334.5804846085318</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15785,28 +15914,28 @@
         <v>0.1217</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5094764419399991</v>
+        <v>0.5104526317817103</v>
       </c>
       <c r="J3" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K3" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3960653757600602</v>
+        <v>0.4014998078970655</v>
       </c>
       <c r="M3" t="n">
-        <v>3.68690490229097</v>
+        <v>3.660017338494162</v>
       </c>
       <c r="N3" t="n">
-        <v>21.92210108854068</v>
+        <v>21.7398152122309</v>
       </c>
       <c r="O3" t="n">
-        <v>4.682104344046668</v>
+        <v>4.662597474823546</v>
       </c>
       <c r="P3" t="n">
-        <v>334.0061311454411</v>
+        <v>333.9955780626443</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15863,28 +15992,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4375769858157667</v>
+        <v>0.4427297912951794</v>
       </c>
       <c r="J4" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K4" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2512194103622026</v>
+        <v>0.2587926169852702</v>
       </c>
       <c r="M4" t="n">
-        <v>3.807217890056311</v>
+        <v>3.791534012749218</v>
       </c>
       <c r="N4" t="n">
-        <v>31.60976312289693</v>
+        <v>31.42182090516775</v>
       </c>
       <c r="O4" t="n">
-        <v>5.622256052768935</v>
+        <v>5.605517006054638</v>
       </c>
       <c r="P4" t="n">
-        <v>340.2926974287</v>
+        <v>340.2370025318738</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15941,28 +16070,28 @@
         <v>0.1175</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4034353527173896</v>
+        <v>0.4065016085620383</v>
       </c>
       <c r="J5" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K5" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3194099384262599</v>
+        <v>0.3265117118471181</v>
       </c>
       <c r="M5" t="n">
-        <v>3.270510928811928</v>
+        <v>3.253252517735842</v>
       </c>
       <c r="N5" t="n">
-        <v>19.20861240785691</v>
+        <v>19.07751581677601</v>
       </c>
       <c r="O5" t="n">
-        <v>4.382763101954851</v>
+        <v>4.367781566971499</v>
       </c>
       <c r="P5" t="n">
-        <v>335.1626220415509</v>
+        <v>335.1294758366745</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16019,28 +16148,28 @@
         <v>0.1334</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4971826166281393</v>
+        <v>0.4981989825764105</v>
       </c>
       <c r="J6" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K6" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4405421175712704</v>
+        <v>0.4461743272269122</v>
       </c>
       <c r="M6" t="n">
-        <v>3.130471179791396</v>
+        <v>3.108224695019262</v>
       </c>
       <c r="N6" t="n">
-        <v>17.38692353641217</v>
+        <v>17.2440860052397</v>
       </c>
       <c r="O6" t="n">
-        <v>4.169763007223812</v>
+        <v>4.152599909121959</v>
       </c>
       <c r="P6" t="n">
-        <v>336.7882446741215</v>
+        <v>336.7772569874163</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16097,28 +16226,28 @@
         <v>0.1117</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5658065686229152</v>
+        <v>0.5607207029728234</v>
       </c>
       <c r="J7" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K7" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4526152639763521</v>
+        <v>0.4519713453851738</v>
       </c>
       <c r="M7" t="n">
-        <v>3.801809278612834</v>
+        <v>3.799101317267325</v>
       </c>
       <c r="N7" t="n">
-        <v>21.44422560219622</v>
+        <v>21.33789380674206</v>
       </c>
       <c r="O7" t="n">
-        <v>4.630791034175071</v>
+        <v>4.619295812863911</v>
       </c>
       <c r="P7" t="n">
-        <v>336.7736043196692</v>
+        <v>336.8285651331561</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16175,28 +16304,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4437152832558641</v>
+        <v>0.4304152729586833</v>
       </c>
       <c r="J8" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K8" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2352474128380827</v>
+        <v>0.2252217496163169</v>
       </c>
       <c r="M8" t="n">
-        <v>4.883920946772458</v>
+        <v>4.899583809612258</v>
       </c>
       <c r="N8" t="n">
-        <v>35.4499629101701</v>
+        <v>35.67043792736533</v>
       </c>
       <c r="O8" t="n">
-        <v>5.953987143937254</v>
+        <v>5.972473350912948</v>
       </c>
       <c r="P8" t="n">
-        <v>336.8183185443788</v>
+        <v>336.9620375908027</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16234,7 +16363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I350"/>
+  <dimension ref="A1:I353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32687,6 +32816,147 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-35.4543635525465,174.42793661752322</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-35.45510462300066,174.42811098274126</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-35.455716888545915,174.42863523405128</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-35.456282343178586,174.42924022230235</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-35.45672258411687,174.4299857682065</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-35.45706258914552,174.4307979765078</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-35.45725472651737,174.43169596405178</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-35.454362386920884,174.42794363589803</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-35.45510096014778,174.428122600167</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-35.45571139133335,174.42864354544957</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-35.45627151840803,174.42925153683535</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-35.456712708963146,174.42999327452546</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-35.45705516264104,174.43080069655915</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-35.45723677596604,174.43169898492124</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-35.45436199240136,174.42794601134793</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-35.45510245122076,174.4281178709496</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-35.45570702756628,174.4286501431567</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-35.45627021669506,174.42925289744358</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-35.45671691930005,174.42999007415716</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-35.457060862051456,174.43079860907793</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-35.45723677596604,174.43169898492124</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0078/nzd0078.xlsx
+++ b/data/nzd0078/nzd0078.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I353"/>
+  <dimension ref="A1:I354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12089,6 +12089,39 @@
         <v>341.56</v>
       </c>
       <c r="I353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:17+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>348.94</v>
+      </c>
+      <c r="C354" t="n">
+        <v>349.61</v>
+      </c>
+      <c r="D354" t="n">
+        <v>356.94</v>
+      </c>
+      <c r="E354" t="n">
+        <v>350.16</v>
+      </c>
+      <c r="F354" t="n">
+        <v>352.66</v>
+      </c>
+      <c r="G354" t="n">
+        <v>349.95</v>
+      </c>
+      <c r="H354" t="n">
+        <v>343.19</v>
+      </c>
+      <c r="I354" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12105,7 +12138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15668,6 +15701,16 @@
       </c>
       <c r="B356" t="n">
         <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -15836,28 +15879,28 @@
         <v>0.1223</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4656246666595238</v>
+        <v>0.4666187436121533</v>
       </c>
       <c r="J2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3381830128222215</v>
+        <v>0.3404735234219904</v>
       </c>
       <c r="M2" t="n">
-        <v>3.796929177506129</v>
+        <v>3.789861497768614</v>
       </c>
       <c r="N2" t="n">
-        <v>23.74783818773758</v>
+        <v>23.68931646072478</v>
       </c>
       <c r="O2" t="n">
-        <v>4.8731753700988</v>
+        <v>4.867167190545726</v>
       </c>
       <c r="P2" t="n">
-        <v>334.5804846085318</v>
+        <v>334.5696927267648</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15914,28 +15957,28 @@
         <v>0.1217</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5104526317817103</v>
+        <v>0.5114697241428319</v>
       </c>
       <c r="J3" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K3" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4014998078970655</v>
+        <v>0.4038762079696826</v>
       </c>
       <c r="M3" t="n">
-        <v>3.660017338494162</v>
+        <v>3.654268004179296</v>
       </c>
       <c r="N3" t="n">
-        <v>21.7398152122309</v>
+        <v>21.68739191729886</v>
       </c>
       <c r="O3" t="n">
-        <v>4.662597474823546</v>
+        <v>4.656972398168026</v>
       </c>
       <c r="P3" t="n">
-        <v>333.9955780626443</v>
+        <v>333.9845363213804</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15992,28 +16035,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4427297912951794</v>
+        <v>0.4453923940665593</v>
       </c>
       <c r="J4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2587926169852702</v>
+        <v>0.261933736807115</v>
       </c>
       <c r="M4" t="n">
-        <v>3.791534012749218</v>
+        <v>3.789414235713785</v>
       </c>
       <c r="N4" t="n">
-        <v>31.42182090516775</v>
+        <v>31.3956000608623</v>
       </c>
       <c r="O4" t="n">
-        <v>5.605517006054638</v>
+        <v>5.603177675289469</v>
       </c>
       <c r="P4" t="n">
-        <v>340.2370025318738</v>
+        <v>340.2080968277174</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16070,28 +16113,28 @@
         <v>0.1175</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4065016085620383</v>
+        <v>0.4087729548403123</v>
       </c>
       <c r="J5" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K5" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3265117118471181</v>
+        <v>0.3298334147545006</v>
       </c>
       <c r="M5" t="n">
-        <v>3.253252517735842</v>
+        <v>3.252243497246639</v>
       </c>
       <c r="N5" t="n">
-        <v>19.07751581677601</v>
+        <v>19.06916635704753</v>
       </c>
       <c r="O5" t="n">
-        <v>4.367781566971499</v>
+        <v>4.366825661398395</v>
       </c>
       <c r="P5" t="n">
-        <v>335.1294758366745</v>
+        <v>335.1048176847857</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16148,28 +16191,28 @@
         <v>0.1334</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4981989825764105</v>
+        <v>0.4995516153681062</v>
       </c>
       <c r="J6" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K6" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4461743272269122</v>
+        <v>0.4488450784016109</v>
       </c>
       <c r="M6" t="n">
-        <v>3.108224695019262</v>
+        <v>3.104751384907017</v>
       </c>
       <c r="N6" t="n">
-        <v>17.2440860052397</v>
+        <v>17.21144120046009</v>
       </c>
       <c r="O6" t="n">
-        <v>4.152599909121959</v>
+        <v>4.148667400558893</v>
       </c>
       <c r="P6" t="n">
-        <v>336.7772569874163</v>
+        <v>336.7625725576812</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16226,28 +16269,28 @@
         <v>0.1117</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5607207029728234</v>
+        <v>0.5595695731810559</v>
       </c>
       <c r="J7" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K7" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4519713453851738</v>
+        <v>0.4523824916989416</v>
       </c>
       <c r="M7" t="n">
-        <v>3.799101317267325</v>
+        <v>3.795085286916918</v>
       </c>
       <c r="N7" t="n">
-        <v>21.33789380674206</v>
+        <v>21.28918320904731</v>
       </c>
       <c r="O7" t="n">
-        <v>4.619295812863911</v>
+        <v>4.614020287021646</v>
       </c>
       <c r="P7" t="n">
-        <v>336.8285651331561</v>
+        <v>336.8410620093571</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16304,28 +16347,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4304152729586833</v>
+        <v>0.4273660588263503</v>
       </c>
       <c r="J8" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K8" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2252217496163169</v>
+        <v>0.2234450720284296</v>
       </c>
       <c r="M8" t="n">
-        <v>4.899583809612258</v>
+        <v>4.899049334079423</v>
       </c>
       <c r="N8" t="n">
-        <v>35.67043792736533</v>
+        <v>35.65174031466497</v>
       </c>
       <c r="O8" t="n">
-        <v>5.972473350912948</v>
+        <v>5.970907830025931</v>
       </c>
       <c r="P8" t="n">
-        <v>336.9620375908027</v>
+        <v>336.9951404188197</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16363,7 +16406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I353"/>
+  <dimension ref="A1:I354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32957,6 +33000,53 @@
         </is>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:17+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-35.45436199240136,174.42794601134793</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-35.455098464220846,174.4281305164653</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-35.45570153035271,174.42865845455293</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-35.45625884383364,174.42926478486066</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-35.456703063463735,174.43000060627713</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-35.45705136303407,174.43080208821317</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-35.45722221905121,174.43170143468018</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
